--- a/docs/sprintC/PI-2023-24 Self-Assessment_v05_07.06.2024.xlsx
+++ b/docs/sprintC/PI-2023-24 Self-Assessment_v05_07.06.2024.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ABT\Documents\ISEP\UNIDADES-CURRICULARES\LAPR2_2023-2024\05_Integrative-PROJECT_2023-2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francisco\Desktop\lei-24-s2-1dp-g163-github\docs\sprintC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4623E077-78DA-4E8A-87C1-33ED3B607CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBFC68E7-2852-4965-955A-A2E546A0BC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Group and Self Assessment" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="45">
   <si>
     <t>TeamID #</t>
   </si>
@@ -61,9 +61,6 @@
   </si>
   <si>
     <t>List A</t>
-  </si>
-  <si>
-    <t>Student 1</t>
   </si>
   <si>
     <t>Student 2</t>
@@ -844,41 +841,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -889,6 +856,36 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1434,14 +1431,14 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1468,24 +1465,24 @@
     <row r="8" spans="1:13" ht="15.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="E8" s="45" t="s">
+      <c r="E8" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="46"/>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
-      <c r="L8" s="46"/>
-      <c r="M8" s="47"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="59"/>
+      <c r="K8" s="59"/>
+      <c r="L8" s="59"/>
+      <c r="M8" s="60"/>
     </row>
     <row r="9" spans="1:13" ht="105.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="29" t="str">
+      <c r="D9" s="29">
         <f>C10</f>
-        <v>Student 1</v>
+        <v>1230684</v>
       </c>
       <c r="E9" s="30" t="str">
         <f>C11</f>
@@ -1520,32 +1517,44 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="63"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
+      <c r="C10" s="25">
+        <v>1230684</v>
+      </c>
+      <c r="D10" s="53">
+        <v>5</v>
+      </c>
+      <c r="E10" s="26">
+        <v>5</v>
+      </c>
+      <c r="F10" s="27">
+        <v>5</v>
+      </c>
+      <c r="G10" s="27">
+        <v>4</v>
+      </c>
+      <c r="H10" s="27">
+        <v>4</v>
+      </c>
+      <c r="I10" s="27">
+        <v>4</v>
+      </c>
       <c r="J10" s="27"/>
       <c r="K10" s="25"/>
-      <c r="L10" s="35" t="e">
-        <f>AVERAGE(D10:K10)</f>
-        <v>#DIV/0!</v>
+      <c r="L10" s="35">
+        <f t="shared" ref="L10:L17" si="0">AVERAGE(D10:K10)</f>
+        <v>4.5</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="43"/>
+      <c r="B11" s="56"/>
       <c r="C11" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D11" s="7"/>
-      <c r="E11" s="63"/>
+      <c r="E11" s="53"/>
       <c r="F11" s="24"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
@@ -1553,86 +1562,86 @@
       <c r="J11" s="6"/>
       <c r="K11" s="8"/>
       <c r="L11" s="36" t="e">
-        <f>AVERAGE(D11:K11)</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="43"/>
+      <c r="B12" s="56"/>
       <c r="C12" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="7"/>
-      <c r="F12" s="63"/>
+      <c r="F12" s="53"/>
       <c r="G12" s="24"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
       <c r="K12" s="8"/>
       <c r="L12" s="36" t="e">
-        <f>AVERAGE(D12:K12)</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="43"/>
+      <c r="B13" s="56"/>
       <c r="C13" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
-      <c r="G13" s="63"/>
+      <c r="G13" s="53"/>
       <c r="H13" s="24"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
       <c r="K13" s="8"/>
       <c r="L13" s="36" t="e">
-        <f>AVERAGE(D13:K13)</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="43"/>
+      <c r="B14" s="56"/>
       <c r="C14" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="7"/>
-      <c r="H14" s="63"/>
+      <c r="H14" s="53"/>
       <c r="I14" s="24"/>
       <c r="J14" s="6"/>
       <c r="K14" s="8"/>
       <c r="L14" s="36" t="e">
-        <f>AVERAGE(D14:K14)</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="43"/>
+      <c r="B15" s="56"/>
       <c r="C15" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="7"/>
-      <c r="I15" s="63"/>
+      <c r="I15" s="53"/>
       <c r="J15" s="24"/>
       <c r="K15" s="8"/>
       <c r="L15" s="36" t="e">
-        <f>AVERAGE(D15:K15)</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="43"/>
+      <c r="B16" s="56"/>
       <c r="C16" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -1640,17 +1649,17 @@
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
       <c r="I16" s="7"/>
-      <c r="J16" s="63"/>
+      <c r="J16" s="53"/>
       <c r="K16" s="8"/>
       <c r="L16" s="36" t="e">
-        <f>AVERAGE(D16:K16)</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="44"/>
+      <c r="B17" s="57"/>
       <c r="C17" s="28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D17" s="28"/>
       <c r="E17" s="28"/>
@@ -1659,9 +1668,9 @@
       <c r="H17" s="28"/>
       <c r="I17" s="28"/>
       <c r="J17" s="28"/>
-      <c r="K17" s="64"/>
+      <c r="K17" s="54"/>
       <c r="L17" s="37" t="e">
-        <f>AVERAGE(D17:K17)</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1670,255 +1679,255 @@
       <c r="C18" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="33" t="e">
-        <f>AVERAGE(D10:D17)</f>
+      <c r="D18" s="33">
+        <f t="shared" ref="D18:K18" si="1">AVERAGE(D10:D17)</f>
+        <v>5</v>
+      </c>
+      <c r="E18" s="33">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="F18" s="33">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="G18" s="33">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="H18" s="33">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="I18" s="33">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="J18" s="33" t="e">
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E18" s="33" t="e">
-        <f>AVERAGE(E10:E17)</f>
+      <c r="K18" s="34" t="e">
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F18" s="33" t="e">
-        <f>AVERAGE(F10:F17)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G18" s="33" t="e">
-        <f>AVERAGE(G10:G17)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H18" s="33" t="e">
-        <f>AVERAGE(H10:H17)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I18" s="33" t="e">
-        <f>AVERAGE(I10:I17)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J18" s="33" t="e">
-        <f>AVERAGE(J10:J17)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K18" s="34" t="e">
-        <f>AVERAGE(K10:K17)</f>
-        <v>#DIV/0!</v>
-      </c>
       <c r="L18" s="38"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="52" t="s">
+      <c r="A20" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="44"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="46"/>
+      <c r="C21" s="46"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="46"/>
+      <c r="K21" s="46"/>
+      <c r="L21" s="47"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="46"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="46"/>
+      <c r="K22" s="46"/>
+      <c r="L22" s="47"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="46"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="46"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="47"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="45"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="47"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="46"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="46"/>
+      <c r="K25" s="46"/>
+      <c r="L25" s="47"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="45">
+        <v>0</v>
+      </c>
+      <c r="B26" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="53"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="54"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="55" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="56"/>
-      <c r="K21" s="56"/>
-      <c r="L21" s="57"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="58" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="56"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="56"/>
-      <c r="H22" s="56"/>
-      <c r="I22" s="56"/>
-      <c r="J22" s="56"/>
-      <c r="K22" s="56"/>
-      <c r="L22" s="57"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="56"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="56"/>
-      <c r="I23" s="56"/>
-      <c r="J23" s="56"/>
-      <c r="K23" s="56"/>
-      <c r="L23" s="57"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="55"/>
-      <c r="B24" s="56"/>
-      <c r="C24" s="56"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="56"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="56"/>
-      <c r="J24" s="56"/>
-      <c r="K24" s="56"/>
-      <c r="L24" s="57"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="59" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="56"/>
-      <c r="C25" s="56"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="56"/>
-      <c r="J25" s="56"/>
-      <c r="K25" s="56"/>
-      <c r="L25" s="57"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="55">
-        <v>0</v>
-      </c>
-      <c r="B26" s="56" t="s">
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="47"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="45">
+        <v>1</v>
+      </c>
+      <c r="B27" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="56"/>
-      <c r="K26" s="56"/>
-      <c r="L26" s="57"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="55">
-        <v>1</v>
-      </c>
-      <c r="B27" s="56" t="s">
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="47"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="45">
+        <v>2</v>
+      </c>
+      <c r="B28" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="56"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="56"/>
-      <c r="K27" s="56"/>
-      <c r="L27" s="57"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="55">
-        <v>2</v>
-      </c>
-      <c r="B28" s="56" t="s">
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="47"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="45">
+        <v>3</v>
+      </c>
+      <c r="B29" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="56"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="57"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="55">
-        <v>3</v>
-      </c>
-      <c r="B29" s="56" t="s">
+      <c r="C29" s="46"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="46"/>
+      <c r="J29" s="46"/>
+      <c r="K29" s="46"/>
+      <c r="L29" s="47"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="45">
+        <v>4</v>
+      </c>
+      <c r="B30" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="56"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="56"/>
-      <c r="J29" s="56"/>
-      <c r="K29" s="56"/>
-      <c r="L29" s="57"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="55">
-        <v>4</v>
-      </c>
-      <c r="B30" s="56" t="s">
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="46"/>
+      <c r="K30" s="46"/>
+      <c r="L30" s="47"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="45">
+        <v>5</v>
+      </c>
+      <c r="B31" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="56"/>
-      <c r="J30" s="56"/>
-      <c r="K30" s="56"/>
-      <c r="L30" s="57"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="55">
-        <v>5</v>
-      </c>
-      <c r="B31" s="56" t="s">
-        <v>20</v>
-      </c>
-      <c r="C31" s="56"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="56"/>
-      <c r="F31" s="56"/>
-      <c r="G31" s="56"/>
-      <c r="H31" s="56"/>
-      <c r="I31" s="56"/>
-      <c r="J31" s="56"/>
-      <c r="K31" s="56"/>
-      <c r="L31" s="57"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="46"/>
+      <c r="K31" s="46"/>
+      <c r="L31" s="47"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="60"/>
-      <c r="B32" s="61"/>
-      <c r="C32" s="61"/>
-      <c r="D32" s="61"/>
-      <c r="E32" s="61"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="61"/>
-      <c r="I32" s="61"/>
-      <c r="J32" s="61"/>
-      <c r="K32" s="61"/>
-      <c r="L32" s="62"/>
+      <c r="A32" s="50"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="51"/>
+      <c r="I32" s="51"/>
+      <c r="J32" s="51"/>
+      <c r="K32" s="51"/>
+      <c r="L32" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1949,22 +1958,22 @@
   <sheetData>
     <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="C3" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="D3" s="61" t="s">
         <v>24</v>
-      </c>
-      <c r="D3" s="48" t="s">
-        <v>25</v>
       </c>
       <c r="E3" s="9">
         <v>0</v>
@@ -1986,411 +1995,447 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="43"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="49"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="62"/>
       <c r="E4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="J4" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="12" t="s">
+    </row>
+    <row r="5" spans="1:10" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="56"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="15" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="43"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="15" t="s">
+      <c r="F5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="G5" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="H5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="I5" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="J5" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="13" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="6" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
+      <c r="A6" s="11">
+        <v>15</v>
+      </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="40"/>
       <c r="E6" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="G6" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="H6" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="I6" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="21" t="s">
-        <v>36</v>
-      </c>
       <c r="J6" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
+      <c r="A7" s="11">
+        <v>16</v>
+      </c>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="40"/>
       <c r="E7" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="I7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J7" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
+      <c r="A8" s="11">
+        <v>17</v>
+      </c>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
       <c r="D8" s="40"/>
       <c r="E8" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J8" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
+      <c r="A9" s="11">
+        <v>18</v>
+      </c>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
       <c r="D9" s="40"/>
       <c r="E9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="H9" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="I9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J9" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
+      <c r="A10" s="11">
+        <v>19</v>
+      </c>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
       <c r="D10" s="40"/>
       <c r="E10" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="H10" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="I10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J10" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
+      <c r="A11" s="11">
+        <v>20</v>
+      </c>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
       <c r="D11" s="40"/>
       <c r="E11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="G11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="H11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="I11" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J11" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
+      <c r="A12" s="11">
+        <v>21</v>
+      </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
       <c r="D12" s="40"/>
       <c r="E12" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="G12" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="H12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="I12" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J12" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="18"/>
+      <c r="A13" s="11">
+        <v>22</v>
+      </c>
+      <c r="B13" s="18">
+        <v>1230684</v>
+      </c>
       <c r="C13" s="18"/>
       <c r="D13" s="40"/>
       <c r="E13" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I13" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J13" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
+      <c r="A14" s="11">
+        <v>23</v>
+      </c>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
       <c r="D14" s="40"/>
       <c r="E14" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="G14" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="H14" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="I14" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I14" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J14" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
+      <c r="A15" s="11">
+        <v>24</v>
+      </c>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
       <c r="D15" s="40"/>
       <c r="E15" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="H15" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="I15" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J15" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
+      <c r="A16" s="11">
+        <v>25</v>
+      </c>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
       <c r="D16" s="40"/>
       <c r="E16" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="G16" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="H16" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="I16" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I16" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J16" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="18"/>
+      <c r="A17" s="11">
+        <v>26</v>
+      </c>
+      <c r="B17" s="18">
+        <v>1230684</v>
+      </c>
       <c r="C17" s="18"/>
       <c r="D17" s="40"/>
       <c r="E17" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="H17" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="I17" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I17" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J17" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
+      <c r="A18" s="11">
+        <v>27</v>
+      </c>
       <c r="B18" s="18"/>
       <c r="C18" s="18"/>
       <c r="D18" s="40"/>
       <c r="E18" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="G18" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="H18" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="I18" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I18" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J18" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
-      <c r="B19" s="18"/>
+      <c r="A19" s="11">
+        <v>28</v>
+      </c>
+      <c r="B19" s="18">
+        <v>1230684</v>
+      </c>
       <c r="C19" s="18"/>
       <c r="D19" s="40"/>
       <c r="E19" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="H19" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="I19" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I19" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J19" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
+      <c r="A20" s="11">
+        <v>29</v>
+      </c>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
       <c r="D20" s="40"/>
       <c r="E20" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="G20" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="H20" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="I20" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I20" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J20" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
@@ -2399,22 +2444,22 @@
       <c r="C21" s="18"/>
       <c r="D21" s="40"/>
       <c r="E21" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="H21" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="I21" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I21" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J21" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
@@ -2423,22 +2468,22 @@
       <c r="C22" s="18"/>
       <c r="D22" s="40"/>
       <c r="E22" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="G22" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="H22" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="I22" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I22" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J22" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
@@ -2447,22 +2492,22 @@
       <c r="C23" s="18"/>
       <c r="D23" s="40"/>
       <c r="E23" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="G23" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="H23" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="I23" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J23" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
@@ -2471,22 +2516,22 @@
       <c r="C24" s="18"/>
       <c r="D24" s="40"/>
       <c r="E24" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="G24" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="H24" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="I24" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I24" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J24" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
@@ -2495,22 +2540,22 @@
       <c r="C25" s="18"/>
       <c r="D25" s="40"/>
       <c r="E25" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="G25" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="H25" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="I25" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I25" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J25" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
@@ -2519,22 +2564,22 @@
       <c r="C26" s="18"/>
       <c r="D26" s="40"/>
       <c r="E26" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="G26" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="H26" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="I26" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I26" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J26" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
@@ -2543,22 +2588,22 @@
       <c r="C27" s="18"/>
       <c r="D27" s="40"/>
       <c r="E27" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="G27" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="H27" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="I27" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I27" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J27" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
@@ -2567,22 +2612,22 @@
       <c r="C28" s="18"/>
       <c r="D28" s="40"/>
       <c r="E28" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F28" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="G28" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="H28" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="I28" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I28" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J28" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
@@ -2591,48 +2636,48 @@
       <c r="C29" s="18"/>
       <c r="D29" s="40"/>
       <c r="E29" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F29" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="G29" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="H29" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="I29" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I29" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J29" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B30" s="18"/>
       <c r="C30" s="18"/>
       <c r="D30" s="40"/>
       <c r="E30" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F30" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="G30" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="H30" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="I30" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I30" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J30" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
@@ -2641,22 +2686,22 @@
       <c r="C31" s="18"/>
       <c r="D31" s="40"/>
       <c r="E31" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="G31" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="H31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H31" s="5" t="s">
+      <c r="I31" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I31" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J31" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -2665,22 +2710,22 @@
       <c r="C32" s="18"/>
       <c r="D32" s="41"/>
       <c r="E32" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F32" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F32" s="16" t="s">
+      <c r="G32" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="G32" s="16" t="s">
+      <c r="H32" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="H32" s="16" t="s">
+      <c r="I32" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="I32" s="16" t="s">
-        <v>36</v>
-      </c>
       <c r="J32" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2717,6 +2762,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005836243B3C47804EAF5FFDD9F066FCC7" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9d21ddf3f0b128e39c9d770c8c903166">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1e3ca88-8ae5-4fd0-ba37-40ce669fcbb0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b0326308c339679ad994635f2c691325" ns2:_="">
     <xsd:import namespace="a1e3ca88-8ae5-4fd0-ba37-40ce669fcbb0"/>
@@ -2900,22 +2960,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D8D82CB-2E6F-4A14-B6B4-DFDD1BBD70FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a1e3ca88-8ae5-4fd0-ba37-40ce669fcbb0"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F61419B8-A98A-41CD-95EE-48A4F975B8D1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23B77F7C-EE47-4FBD-B078-6536C1487A1E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2931,28 +3000,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F61419B8-A98A-41CD-95EE-48A4F975B8D1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D8D82CB-2E6F-4A14-B6B4-DFDD1BBD70FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a1e3ca88-8ae5-4fd0-ba37-40ce669fcbb0"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/docs/sprintC/PI-2023-24 Self-Assessment_v05_07.06.2024.xlsx
+++ b/docs/sprintC/PI-2023-24 Self-Assessment_v05_07.06.2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francisco\Desktop\lei-24-s2-1dp-g163-github\docs\sprintC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBFC68E7-2852-4965-955A-A2E546A0BC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C84A33C-2BD1-4FD7-B23B-DAFD50E8FA06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Group and Self Assessment" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="46">
   <si>
     <t>TeamID #</t>
   </si>
@@ -61,21 +61,6 @@
   </si>
   <si>
     <t>List A</t>
-  </si>
-  <si>
-    <t>Student 2</t>
-  </si>
-  <si>
-    <t>Student 3</t>
-  </si>
-  <si>
-    <t>Student 4</t>
-  </si>
-  <si>
-    <t>Student 5</t>
-  </si>
-  <si>
-    <t>Student 6</t>
   </si>
   <si>
     <t>Student 7</t>
@@ -190,6 +175,24 @@
   </si>
   <si>
     <t>User Manual (LAPR2)</t>
+  </si>
+  <si>
+    <t>Scene Builder</t>
+  </si>
+  <si>
+    <t>Implementing US's</t>
+  </si>
+  <si>
+    <t>Unit Tests</t>
+  </si>
+  <si>
+    <t>UI Interfaces</t>
+  </si>
+  <si>
+    <t>1231502 / 1230605</t>
+  </si>
+  <si>
+    <t>1220804 / 1210527</t>
   </si>
 </sst>
 </file>
@@ -1431,14 +1434,14 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1484,25 +1487,25 @@
         <f>C10</f>
         <v>1230684</v>
       </c>
-      <c r="E9" s="30" t="str">
+      <c r="E9" s="30">
         <f>C11</f>
-        <v>Student 2</v>
-      </c>
-      <c r="F9" s="30" t="str">
+        <v>1231205</v>
+      </c>
+      <c r="F9" s="30">
         <f>C12</f>
-        <v>Student 3</v>
-      </c>
-      <c r="G9" s="30" t="str">
+        <v>1220804</v>
+      </c>
+      <c r="G9" s="30">
         <f>C13</f>
-        <v>Student 4</v>
-      </c>
-      <c r="H9" s="30" t="str">
+        <v>1231502</v>
+      </c>
+      <c r="H9" s="30">
         <f>C14</f>
-        <v>Student 5</v>
-      </c>
-      <c r="I9" s="30" t="str">
+        <v>1230605</v>
+      </c>
+      <c r="I9" s="30">
         <f>C15</f>
-        <v>Student 6</v>
+        <v>1210527</v>
       </c>
       <c r="J9" s="30" t="str">
         <f>C16</f>
@@ -1527,13 +1530,13 @@
         <v>5</v>
       </c>
       <c r="E10" s="26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F10" s="27">
         <v>5</v>
       </c>
       <c r="G10" s="27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H10" s="27">
         <v>4</v>
@@ -1550,98 +1553,158 @@
     </row>
     <row r="11" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56"/>
-      <c r="C11" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
+      <c r="C11" s="6">
+        <v>1231205</v>
+      </c>
+      <c r="D11" s="7">
+        <v>5</v>
+      </c>
+      <c r="E11" s="53">
+        <v>4</v>
+      </c>
+      <c r="F11" s="24">
+        <v>5</v>
+      </c>
+      <c r="G11" s="6">
+        <v>5</v>
+      </c>
+      <c r="H11" s="6">
+        <v>4</v>
+      </c>
+      <c r="I11" s="6">
+        <v>4</v>
+      </c>
       <c r="J11" s="6"/>
       <c r="K11" s="8"/>
-      <c r="L11" s="36" t="e">
+      <c r="L11" s="36">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="56"/>
-      <c r="C12" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
+      <c r="C12" s="6">
+        <v>1220804</v>
+      </c>
+      <c r="D12" s="6">
+        <v>5</v>
+      </c>
+      <c r="E12" s="7">
+        <v>4</v>
+      </c>
+      <c r="F12" s="53">
+        <v>5</v>
+      </c>
+      <c r="G12" s="24">
+        <v>4</v>
+      </c>
+      <c r="H12" s="6">
+        <v>4</v>
+      </c>
+      <c r="I12" s="6">
+        <v>4</v>
+      </c>
       <c r="J12" s="6"/>
       <c r="K12" s="8"/>
-      <c r="L12" s="36" t="e">
+      <c r="L12" s="36">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>4.333333333333333</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56"/>
-      <c r="C13" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="6"/>
+      <c r="C13" s="6">
+        <v>1231502</v>
+      </c>
+      <c r="D13" s="6">
+        <v>5</v>
+      </c>
+      <c r="E13" s="6">
+        <v>5</v>
+      </c>
+      <c r="F13" s="7">
+        <v>5</v>
+      </c>
+      <c r="G13" s="53">
+        <v>5</v>
+      </c>
+      <c r="H13" s="24">
+        <v>4</v>
+      </c>
+      <c r="I13" s="6">
+        <v>4</v>
+      </c>
       <c r="J13" s="6"/>
       <c r="K13" s="8"/>
-      <c r="L13" s="36" t="e">
+      <c r="L13" s="36">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>4.666666666666667</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="56"/>
-      <c r="C14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="24"/>
+      <c r="C14" s="6">
+        <v>1230605</v>
+      </c>
+      <c r="D14" s="6">
+        <v>5</v>
+      </c>
+      <c r="E14" s="6">
+        <v>4</v>
+      </c>
+      <c r="F14" s="6">
+        <v>5</v>
+      </c>
+      <c r="G14" s="7">
+        <v>5</v>
+      </c>
+      <c r="H14" s="53">
+        <v>3</v>
+      </c>
+      <c r="I14" s="24">
+        <v>4</v>
+      </c>
       <c r="J14" s="6"/>
       <c r="K14" s="8"/>
-      <c r="L14" s="36" t="e">
+      <c r="L14" s="36">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>4.333333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56"/>
-      <c r="C15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="53"/>
+      <c r="C15" s="6">
+        <v>1210527</v>
+      </c>
+      <c r="D15" s="6">
+        <v>5</v>
+      </c>
+      <c r="E15" s="6">
+        <v>5</v>
+      </c>
+      <c r="F15" s="6">
+        <v>5</v>
+      </c>
+      <c r="G15" s="6">
+        <v>5</v>
+      </c>
+      <c r="H15" s="7">
+        <v>5</v>
+      </c>
+      <c r="I15" s="53">
+        <v>3</v>
+      </c>
       <c r="J15" s="24"/>
       <c r="K15" s="8"/>
-      <c r="L15" s="36" t="e">
+      <c r="L15" s="36">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>4.666666666666667</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="56"/>
       <c r="C16" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -1659,7 +1722,7 @@
     <row r="17" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="57"/>
       <c r="C17" s="28" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D17" s="28"/>
       <c r="E17" s="28"/>
@@ -1685,7 +1748,7 @@
       </c>
       <c r="E18" s="33">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="F18" s="33">
         <f t="shared" si="1"/>
@@ -1693,7 +1756,7 @@
       </c>
       <c r="G18" s="33">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="H18" s="33">
         <f t="shared" si="1"/>
@@ -1701,7 +1764,7 @@
       </c>
       <c r="I18" s="33">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="J18" s="33" t="e">
         <f t="shared" si="1"/>
@@ -1715,7 +1778,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="42" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B20" s="43"/>
       <c r="C20" s="43"/>
@@ -1731,7 +1794,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="45" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B21" s="46"/>
       <c r="C21" s="46"/>
@@ -1747,7 +1810,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="48" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B22" s="46"/>
       <c r="C22" s="46"/>
@@ -1763,7 +1826,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="45" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B23" s="46"/>
       <c r="C23" s="46"/>
@@ -1793,7 +1856,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="49" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B25" s="46"/>
       <c r="C25" s="46"/>
@@ -1812,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="B26" s="46" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C26" s="46"/>
       <c r="D26" s="46"/>
@@ -1830,7 +1893,7 @@
         <v>1</v>
       </c>
       <c r="B27" s="46" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C27" s="46"/>
       <c r="D27" s="46"/>
@@ -1848,7 +1911,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="46" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C28" s="46"/>
       <c r="D28" s="46"/>
@@ -1866,7 +1929,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="46" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C29" s="46"/>
       <c r="D29" s="46"/>
@@ -1884,7 +1947,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="46" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C30" s="46"/>
       <c r="D30" s="46"/>
@@ -1902,7 +1965,7 @@
         <v>5</v>
       </c>
       <c r="B31" s="46" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C31" s="46"/>
       <c r="D31" s="46"/>
@@ -1958,22 +2021,22 @@
   <sheetData>
     <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="19" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="55" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C3" s="63" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D3" s="61" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E3" s="9">
         <v>0</v>
@@ -2000,22 +2063,22 @@
       <c r="C4" s="64"/>
       <c r="D4" s="62"/>
       <c r="E4" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="12" t="s">
         <v>25</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -2024,204 +2087,224 @@
       <c r="C5" s="64"/>
       <c r="D5" s="62"/>
       <c r="E5" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="13" t="s">
         <v>31</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>15</v>
       </c>
-      <c r="B6" s="18"/>
+      <c r="B6" s="18">
+        <v>1231502</v>
+      </c>
       <c r="C6" s="18"/>
       <c r="D6" s="40"/>
       <c r="E6" s="20" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F6" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G6" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="I6" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>16</v>
       </c>
-      <c r="B7" s="18"/>
+      <c r="B7" s="18">
+        <v>1230684</v>
+      </c>
       <c r="C7" s="18"/>
-      <c r="D7" s="40"/>
+      <c r="D7" s="40" t="s">
+        <v>44</v>
+      </c>
       <c r="E7" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J7" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>17</v>
       </c>
-      <c r="B8" s="18"/>
+      <c r="B8" s="18">
+        <v>1220804</v>
+      </c>
       <c r="C8" s="18"/>
       <c r="D8" s="40"/>
       <c r="E8" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J8" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>18</v>
       </c>
-      <c r="B9" s="18"/>
+      <c r="B9" s="18">
+        <v>1220804</v>
+      </c>
       <c r="C9" s="18"/>
-      <c r="D9" s="40"/>
+      <c r="D9" s="40">
+        <v>1230684</v>
+      </c>
       <c r="E9" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J9" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>19</v>
       </c>
-      <c r="B10" s="18"/>
+      <c r="B10" s="18">
+        <v>1231205</v>
+      </c>
       <c r="C10" s="18"/>
-      <c r="D10" s="40"/>
+      <c r="D10" s="40" t="s">
+        <v>45</v>
+      </c>
       <c r="E10" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <v>20</v>
       </c>
-      <c r="B11" s="18"/>
+      <c r="B11" s="18">
+        <v>1231205</v>
+      </c>
       <c r="C11" s="18"/>
       <c r="D11" s="40"/>
       <c r="E11" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J11" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>21</v>
       </c>
-      <c r="B12" s="18"/>
+      <c r="B12" s="18">
+        <v>1210527</v>
+      </c>
       <c r="C12" s="18"/>
       <c r="D12" s="40"/>
       <c r="E12" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J12" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
@@ -2234,100 +2317,106 @@
       <c r="C13" s="18"/>
       <c r="D13" s="40"/>
       <c r="E13" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J13" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
         <v>23</v>
       </c>
-      <c r="B14" s="18"/>
+      <c r="B14" s="18">
+        <v>1231502</v>
+      </c>
       <c r="C14" s="18"/>
       <c r="D14" s="40"/>
       <c r="E14" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J14" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
         <v>24</v>
       </c>
-      <c r="B15" s="18"/>
+      <c r="B15" s="18">
+        <v>1231205</v>
+      </c>
       <c r="C15" s="18"/>
       <c r="D15" s="40"/>
       <c r="E15" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J15" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
         <v>25</v>
       </c>
-      <c r="B16" s="18"/>
+      <c r="B16" s="18">
+        <v>1210527</v>
+      </c>
       <c r="C16" s="18"/>
       <c r="D16" s="40"/>
       <c r="E16" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J16" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J16" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
@@ -2340,48 +2429,50 @@
       <c r="C17" s="18"/>
       <c r="D17" s="40"/>
       <c r="E17" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J17" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J17" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
         <v>27</v>
       </c>
-      <c r="B18" s="18"/>
+      <c r="B18" s="18">
+        <v>1231502</v>
+      </c>
       <c r="C18" s="18"/>
       <c r="D18" s="40"/>
       <c r="E18" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F18" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J18" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J18" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
@@ -2392,146 +2483,170 @@
         <v>1230684</v>
       </c>
       <c r="C19" s="18"/>
-      <c r="D19" s="40"/>
+      <c r="D19" s="40">
+        <v>1231205</v>
+      </c>
       <c r="E19" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F19" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J19" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J19" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
         <v>29</v>
       </c>
-      <c r="B20" s="18"/>
+      <c r="B20" s="18">
+        <v>1230684</v>
+      </c>
       <c r="C20" s="18"/>
       <c r="D20" s="40"/>
       <c r="E20" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F20" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J20" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J20" s="22" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="21" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
-      <c r="B21" s="18"/>
+      <c r="A21" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="18">
+        <v>1231205</v>
+      </c>
       <c r="C21" s="18"/>
       <c r="D21" s="40"/>
       <c r="E21" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J21" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J21" s="22" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="22" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="B22" s="18"/>
+      <c r="A22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="18">
+        <v>1230684</v>
+      </c>
       <c r="C22" s="18"/>
-      <c r="D22" s="40"/>
+      <c r="D22" s="40">
+        <v>1220804</v>
+      </c>
       <c r="E22" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J22" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J22" s="22" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="23" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="18"/>
+      <c r="A23" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="18">
+        <v>1230605</v>
+      </c>
       <c r="C23" s="18"/>
       <c r="D23" s="40"/>
       <c r="E23" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F23" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J23" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J23" s="22" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="24" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="18"/>
+      <c r="A24" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="18">
+        <v>1220804</v>
+      </c>
       <c r="C24" s="18"/>
-      <c r="D24" s="40"/>
+      <c r="D24" s="40">
+        <v>1230684</v>
+      </c>
       <c r="E24" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F24" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J24" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J24" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
@@ -2540,22 +2655,22 @@
       <c r="C25" s="18"/>
       <c r="D25" s="40"/>
       <c r="E25" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J25" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J25" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
@@ -2564,22 +2679,22 @@
       <c r="C26" s="18"/>
       <c r="D26" s="40"/>
       <c r="E26" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F26" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J26" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J26" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
@@ -2588,22 +2703,22 @@
       <c r="C27" s="18"/>
       <c r="D27" s="40"/>
       <c r="E27" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F27" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J27" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J27" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
@@ -2612,22 +2727,22 @@
       <c r="C28" s="18"/>
       <c r="D28" s="40"/>
       <c r="E28" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F28" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J28" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J28" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
@@ -2636,48 +2751,48 @@
       <c r="C29" s="18"/>
       <c r="D29" s="40"/>
       <c r="E29" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F29" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J29" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J29" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B30" s="18"/>
       <c r="C30" s="18"/>
       <c r="D30" s="40"/>
       <c r="E30" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F30" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J30" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J30" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
@@ -2686,22 +2801,22 @@
       <c r="C31" s="18"/>
       <c r="D31" s="40"/>
       <c r="E31" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J31" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J31" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -2710,22 +2825,22 @@
       <c r="C32" s="18"/>
       <c r="D32" s="41"/>
       <c r="E32" s="15" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F32" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="J32" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="G32" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="H32" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="I32" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="J32" s="22" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2768,15 +2883,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005836243B3C47804EAF5FFDD9F066FCC7" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9d21ddf3f0b128e39c9d770c8c903166">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1e3ca88-8ae5-4fd0-ba37-40ce669fcbb0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b0326308c339679ad994635f2c691325" ns2:_="">
     <xsd:import namespace="a1e3ca88-8ae5-4fd0-ba37-40ce669fcbb0"/>
@@ -2960,6 +3066,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D8D82CB-2E6F-4A14-B6B4-DFDD1BBD70FC}">
   <ds:schemaRefs>
@@ -2977,14 +3092,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F61419B8-A98A-41CD-95EE-48A4F975B8D1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23B77F7C-EE47-4FBD-B078-6536C1487A1E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3000,4 +3107,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F61419B8-A98A-41CD-95EE-48A4F975B8D1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>